--- a/basedatos_partidas/salida/descompuestos/07.04.02.010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/07.04.02.010.xlsx
@@ -610,10 +610,10 @@
         <v>0.35</v>
       </c>
       <c r="G12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="13">
@@ -636,10 +636,10 @@
         <v>0.3</v>
       </c>
       <c r="G13" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="H13" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="14">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>57.24</v>
+        <v>57.55</v>
       </c>
     </row>
     <row r="16">
@@ -873,7 +873,7 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>72.05</v>
+        <v>72.36</v>
       </c>
       <c r="H26" t="n">
         <v>0.72</v>
@@ -892,7 +892,7 @@
       </c>
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="5" t="n">
-        <v>72.77</v>
+        <v>73.08</v>
       </c>
     </row>
   </sheetData>
